--- a/attendance_records.xlsx
+++ b/attendance_records.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Employee ID</t>
   </si>
@@ -26,12 +26,21 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Time</t>
+    <t>In Time</t>
+  </si>
+  <si>
+    <t>Out Time</t>
+  </si>
+  <si>
+    <t>Total Hours</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
+    <t>Leave Reason</t>
+  </si>
+  <si>
     <t>Latitude</t>
   </si>
   <si>
@@ -39,6 +48,42 @@
   </si>
   <si>
     <t>Location Status</t>
+  </si>
+  <si>
+    <t>EMP001</t>
+  </si>
+  <si>
+    <t>Arjun Sharma</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>26-06-2026</t>
+  </si>
+  <si>
+    <t>09:02:13</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Work From Home</t>
+  </si>
+  <si>
+    <t>12.881439535614872</t>
+  </si>
+  <si>
+    <t>80.07291868039613</t>
+  </si>
+  <si>
+    <t>Outside Office</t>
+  </si>
+  <si>
+    <t>09:02:30</t>
+  </si>
+  <si>
+    <t>0h 0m</t>
   </si>
 </sst>
 </file>
@@ -109,9 +154,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -120,18 +171,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="21.484375" customWidth="true"/>
-    <col min="2" max="2" width="21.484375" customWidth="true"/>
-    <col min="3" max="3" width="21.484375" customWidth="true"/>
-    <col min="4" max="4" width="21.484375" customWidth="true"/>
-    <col min="5" max="5" width="21.484375" customWidth="true"/>
-    <col min="6" max="6" width="21.484375" customWidth="true"/>
-    <col min="7" max="7" width="21.484375" customWidth="true"/>
-    <col min="8" max="8" width="21.484375" customWidth="true"/>
-    <col min="9" max="9" width="21.484375" customWidth="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.45703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.33984375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.16796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.421875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.421875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.92578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.6875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="14.1640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="11.25"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="16.1953125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.5390625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -162,6 +216,15 @@
       <c r="I1" t="s" s="1">
         <v>8</v>
       </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s" s="1">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
